--- a/public/documents/pieces-defense/RF-fichiers-evenement-reglement.xlsx
+++ b/public/documents/pieces-defense/RF-fichiers-evenement-reglement.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Reglements par mode" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Triangulation" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Types evenements E" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Articles vs CA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1812,4 +1813,230 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Articles annexe B (fisc)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Articles annexe C (fisc)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Lignes detail (notre relecture)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CA annexe C (fisc) EUR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CA relecture - tickets EUR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CA relecture - ligne par ligne EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>40218</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>38479</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>33222</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>403370.42</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>403370.42</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>403370.38</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>39998</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>38219</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>32760</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>438281.12</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>438031.42</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>438325.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>39132</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>37446</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>31793</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>435594.96</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>434839.81</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>435696.04</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lecture : le NOMBRE D'ARTICLES varie selon l'export (annexe B, annexe C, notre relecture),</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mais le CHIFFRE D'AFFAIRES reste du meme ordre. Exemple 2022-2023 : 40 218 articles (annexe B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>et 38 479 articles (annexe C) donnent le MEME CA de 403 370,42 EUR (table XIII de la proposition).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1 739 articles d'ecart = 0 EUR d'ecart. Notre relecture du detail confirme 403 370,42 EUR au centime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Exercices 2023-2024 et 2024-2025 : la relecture (colonne tickets) concorde a MOINS DE 0,2 % avec</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>l'annexe C du service (ecart de 250 EUR et 755 EUR sur ~438 000 et ~435 000 EUR). Cet ecart tient</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aux avoirs et aux tickets de bord de periode entre deux exports faits a des dates differentes ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>il ne traduit aucune recette manquante (et reste tres inferieur a la marge d'arrondi habituelle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Methode : 'lignes detail' = nombre de lignes du fichier ; 'CA tickets' = somme des Tot_ttc par</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ticket unique (NET de remises) = chiffre de reference ; 'CA ligne par ligne' = somme(quantite x</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>prix unitaire), controle BRUT hors remises (d'ou un leger ecart les annees a remises).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source : annexes C-1 a C-3 (detail des tickets) de la caisse certifiee. Calcul reproductible.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>